--- a/apps/web/public/importmallar/importmall-struktur.xlsx
+++ b/apps/web/public/importmallar/importmall-struktur.xlsx
@@ -70,7 +70,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Sekvensnumret (heltal större än 0) på en av den överordnade artikelns operationer, som materialet dras vid. Tom cell, eller en operation som inte finns, ger ingen koppling — materialet dras vid slutrapporteringen (varning). En kalkyloperation ger ett fel.</t>
+          <t xml:space="preserve">Sekvensnumret (heltal större än 0) på en av den överordnade artikelns operationer, som materialet dras vid. Tom cell, eller en operation som inte finns, ger ingen koppling — materialet dras då i takt med inleveransen av färdiga varor (en operation som inte finns ger en varning). En kalkyloperation ger ett fel.</t>
         </r>
       </text>
     </comment>
@@ -149,7 +149,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -158,6 +158,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -169,10 +170,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="17" customWidth="1"/>
-    <col min="2" max="2" width="19" customWidth="1"/>
+    <col min="1" max="1" width="17" customWidth="1" style="4"/>
+    <col min="2" max="2" width="19" customWidth="1" style="4"/>
     <col min="3" max="3" width="14" customWidth="1"/>
-    <col min="4" max="4" width="14" customWidth="1"/>
+    <col min="4" max="4" width="14" customWidth="1" style="4"/>
     <col min="5" max="5" width="14" customWidth="1"/>
     <col min="6" max="6" width="22" customWidth="1"/>
     <col min="7" max="7" width="16" customWidth="1"/>
@@ -254,66 +255,51 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kolumner du inte behöver kan tas bort eller lämnas tomma, och kolumnernas ordning spelar ingen roll.</t>
+          <t xml:space="preserve">Ta bort kolumner du inte använder. Kolumnernas ordning spelar ingen roll.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t xml:space="preserve">En tom cell lämnar normalt värdet orört på en befintlig post, utom i kolumner där tomt betyder något: Huvudleverantör och Staffel: från antal/Staffel: pris (Inköpspriser), Partiformningsregel (Artiklar) samt Kalkyl och Tidsenhet med Uppdatera befintliga operationer (Operationer). Vad tomt betyder står vid varje kolumn.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
           <t xml:space="preserve">Tal skrivs med decimalkomma eller punkt. Obligatoriska kolumner måste finnas med och vara ifyllda på varje rad.</t>
         </is>
       </c>
     </row>
-    <row r="5"/>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+    <row r="6"/>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Kolumn</t>
         </is>
       </c>
-      <c r="B6" s="1" t="inlineStr">
+      <c r="B7" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Obligatorisk</t>
         </is>
       </c>
-      <c r="C6" s="1" t="inlineStr">
+      <c r="C7" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Förklaring</t>
         </is>
       </c>
-      <c r="D6" s="1" t="inlineStr">
+      <c r="D7" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Exempel</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Artikelnummer</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ja</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Den överordnade (tillverkade) artikeln — måste redan finnas i artikelregistret; importera artiklarna först. En artikel som inte är tillverkad ger en varning.</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SB-1200</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Komponentnummer</t>
+          <t xml:space="preserve">Artikelnummer</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -323,19 +309,19 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Den ingående artikeln. Måste finnas i artikelregistret om inte Skapa saknade artiklar är ikryssat — då skapas den ur radens egna kolumner. Samma komponent kan bara ligga en gång per artikel: finns den redan i strukturen blir raden ett fel (eller hoppas över med Hoppa över rader som redan finns). En artikel kan inte ingå i sin egen struktur, inte heller via flera led.</t>
+          <t xml:space="preserve">Den överordnade (tillverkade) artikeln — måste redan finnas i artikelregistret; importera artiklarna först. En artikel som inte är tillverkad ger en varning.</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PL-2-1500</t>
+          <t xml:space="preserve">SB-1200</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Antal</t>
+          <t xml:space="preserve">Komponentnummer</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -345,41 +331,41 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Antal av komponenten per en enhet av den överordnade artikeln, större än 0, decimalkomma eller punkt. Anges i kolumnen Enhet (annars komponentens grundenhet) och lagras alltid i grundenheten.</t>
+          <t xml:space="preserve">Den ingående artikeln. Måste finnas i artikelregistret om inte Skapa saknade artiklar är ikryssat — då skapas den ur radens egna kolumner. Samma komponent kan bara ligga en gång per artikel: finns den redan i strukturen blir raden ett fel (eller hoppas över med Hoppa över rader som redan finns). En artikel kan inte ingå i sin egen struktur, inte heller via flera led.</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">PL-2-1500</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Enhet</t>
+          <t xml:space="preserve">Antal</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">En av komponentens enheter: grundenheten eller en upplagd alternativ enhet (annars ett fel). Tom cell betyder grundenheten. För en komponent som skapas av importen blir det i stället den nya artikelns grundenhet (tom = st; en okänd kod skapas).</t>
+          <t xml:space="preserve">Antal av komponenten per en enhet av den överordnade artikeln, större än 0, decimalkomma eller punkt. Anges i kolumnen Enhet (annars komponentens grundenhet) och lagras alltid i grundenheten.</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">st</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Operation</t>
+          <t xml:space="preserve">Enhet</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -389,19 +375,19 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sekvensnumret (heltal större än 0) på en av den överordnade artikelns operationer, som materialet dras vid. Tom cell, eller en operation som inte finns, ger ingen koppling — materialet dras vid slutrapporteringen (varning). En kalkyloperation ger ett fel.</t>
+          <t xml:space="preserve">En av komponentens enheter: grundenheten eller en upplagd alternativ enhet (annars ett fel). Tom cell betyder grundenheten. För en komponent som skapas av importen blir det i stället den nya artikelns grundenhet (tom = st; en okänd kod skapas).</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">st</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Komponentbenämning</t>
+          <t xml:space="preserve">Operation</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -411,19 +397,19 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Läses bara för komponenter som saknas i registret när Skapa saknade artiklar är ikryssat — då obligatorisk, max 255 tecken. Befintliga artiklar ändras aldrig av strukturimporten.</t>
+          <t xml:space="preserve">Sekvensnumret (heltal större än 0) på en av den överordnade artikelns operationer, som materialet dras vid. Tom cell, eller en operation som inte finns, ger ingen koppling — materialet dras då i takt med inleveransen av färdiga varor (en operation som inte finns ger en varning). En kalkyloperation ger ett fel.</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Plåt 2 mm 1500×3000</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Komponenttyp</t>
+          <t xml:space="preserve">Komponentbenämning</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -433,32 +419,54 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Artikeltyp för en komponent som skapas: Tillverkad (även M), Köpt (även P eller K), Tjänst (även Lego) eller Fiktiv (även F) — Fiktiv ger en tillverkad fantomartikel. Tom cell ger guidens Standardtyp, annars Köpt. Läses bara med Skapa saknade artiklar.</t>
+          <t xml:space="preserve">Läses bara för komponenter som saknas i registret när Skapa saknade artiklar är ikryssat — då obligatorisk, max 255 tecken. Befintliga artiklar ändras aldrig av strukturimporten.</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Köpt</t>
+          <t xml:space="preserve">Plåt 2 mm 1500×3000</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">Komponenttyp</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nej</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Artikeltyp för en komponent som skapas: Tillverkad (även M), Köpt (även P eller K), Tjänst (även Lego) eller Fiktiv (även F) — Fiktiv ger en tillverkad fantomartikel. Tom cell ger guidens Standardtyp, annars Köpt. Läses bara med Skapa saknade artiklar.</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Köpt</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Komponentens standardpris</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Standardkostnad per grundenhet för en komponent som skapas, decimalkomma eller punkt, aldrig negativ. Läses bara med Skapa saknade artiklar.</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">890</t>
         </is>

--- a/apps/web/public/importmallar/importmall-struktur.xlsx
+++ b/apps/web/public/importmallar/importmall-struktur.xlsx
@@ -82,11 +82,23 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
+          <t xml:space="preserve">Radens position på ritningen, max 20 tecken (siffror eller text). Visas i strukturen på artikelkortets Beredning-flik. Med Uppdatera befintliga strukturrader lämnar en tom cell det sparade värdet orört.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
           <t xml:space="preserve">Läses bara för komponenter som saknas i registret när Skapa saknade artiklar är ikryssat — då obligatorisk, max 255 tecken. Befintliga artiklar ändras aldrig av strukturimporten.</t>
         </r>
       </text>
     </comment>
-    <comment ref="G1" authorId="0">
+    <comment ref="H1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -98,7 +110,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H1" authorId="0">
+    <comment ref="I1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -175,9 +187,10 @@
     <col min="3" max="3" width="14" customWidth="1"/>
     <col min="4" max="4" width="14" customWidth="1" style="4"/>
     <col min="5" max="5" width="14" customWidth="1"/>
-    <col min="6" max="6" width="22" customWidth="1"/>
-    <col min="7" max="7" width="16" customWidth="1"/>
-    <col min="8" max="8" width="29" customWidth="1"/>
+    <col min="6" max="6" width="14" customWidth="1" style="4"/>
+    <col min="7" max="7" width="22" customWidth="1"/>
+    <col min="8" max="8" width="16" customWidth="1"/>
+    <col min="9" max="9" width="29" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -208,15 +221,20 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t xml:space="preserve">Pos.</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t xml:space="preserve">Komponentbenämning</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Komponenttyp</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Komponentens standardpris</t>
         </is>
@@ -409,7 +427,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Komponentbenämning</t>
+          <t xml:space="preserve">Pos.</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -419,19 +437,19 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Läses bara för komponenter som saknas i registret när Skapa saknade artiklar är ikryssat — då obligatorisk, max 255 tecken. Befintliga artiklar ändras aldrig av strukturimporten.</t>
+          <t xml:space="preserve">Radens position på ritningen, max 20 tecken (siffror eller text). Visas i strukturen på artikelkortets Beredning-flik. Med Uppdatera befintliga strukturrader lämnar en tom cell det sparade värdet orört.</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Plåt 2 mm 1500×3000</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Komponenttyp</t>
+          <t xml:space="preserve">Komponentbenämning</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -441,32 +459,54 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Artikeltyp för en komponent som skapas: Tillverkad (även M), Köpt (även P eller K), Tjänst (även Lego) eller Fiktiv (även F) — Fiktiv ger en tillverkad fantomartikel. Tom cell ger guidens Standardtyp, annars Köpt. Läses bara med Skapa saknade artiklar.</t>
+          <t xml:space="preserve">Läses bara för komponenter som saknas i registret när Skapa saknade artiklar är ikryssat — då obligatorisk, max 255 tecken. Befintliga artiklar ändras aldrig av strukturimporten.</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Köpt</t>
+          <t xml:space="preserve">Plåt 2 mm 1500×3000</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">Komponenttyp</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nej</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Artikeltyp för en komponent som skapas: Tillverkad (även M), Köpt (även P eller K), Tjänst (även Lego) eller Fiktiv (även F) — Fiktiv ger en tillverkad fantomartikel. Tom cell ger guidens Standardtyp, annars Köpt. Läses bara med Skapa saknade artiklar.</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Köpt</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Komponentens standardpris</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Nej</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Standardkostnad per grundenhet för en komponent som skapas, decimalkomma eller punkt, aldrig negativ. Läses bara med Skapa saknade artiklar.</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">890</t>
         </is>
